--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104676_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104676_W25.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1935</v>
+        <v>5.7723</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0762</v>
+        <v>4.7638</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1173</v>
+        <v>1.0084</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2732</v>
+        <v>4.2795</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3219</v>
+        <v>2.3125</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9513</v>
+        <v>1.967</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9001</v>
+        <v>5.8653</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3626</v>
+        <v>3.3332</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5375</v>
+        <v>2.5321</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6269</v>
+        <v>-1.5858</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5651</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0711</v>
+        <v>-0.3496</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2873</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3584</v>
+        <v>0.1992</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0761</v>
+        <v>2.07</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7992</v>
+        <v>2.7173</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1157</v>
+        <v>2.9195</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3165</v>
+        <v>-0.2021</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0315</v>
+        <v>1.0393</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1327</v>
+        <v>1.1344</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1012</v>
+        <v>-0.0951</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8063</v>
+        <v>1.7982</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.968</v>
+        <v>0.886</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0294</v>
+        <v>0.8545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.205</v>
+        <v>0.1347</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1389</v>
+        <v>1.1582</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9339</v>
+        <v>-1.0235</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5327</v>
+        <v>-0.5472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4403</v>
+        <v>0.4286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9729</v>
+        <v>-0.9758</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3266</v>
+        <v>1.285</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2601</v>
+        <v>1.2336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8593</v>
+        <v>-1.8323</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0738</v>
+        <v>0.0185</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2389</v>
+        <v>-0.1677</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3127</v>
+        <v>0.1862</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4371</v>
+        <v>0.4358</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6036</v>
+        <v>-0.825</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3048</v>
+        <v>0.2694</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2988</v>
+        <v>-1.0944</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4705</v>
+        <v>-0.4095</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4225</v>
+        <v>-2.1942</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0479</v>
+        <v>1.7847</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2879</v>
+        <v>0.5346</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8077</v>
+        <v>-1.0589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5197000000000001</v>
+        <v>1.5935</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1825</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6149</v>
+        <v>-1.1353</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5676</v>
+        <v>0.1912</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9046</v>
+        <v>-0.1487</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0434</v>
+        <v>-0.2652</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1388</v>
+        <v>0.1165</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8163</v>
+        <v>-1.405</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0697</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7433</v>
+        <v>-0.8871</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4845</v>
+        <v>0.339</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2588</v>
+        <v>-1.2261</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4127</v>
+        <v>-1.4752</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1933</v>
+        <v>-1.4353</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7806</v>
+        <v>-0.0399</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5589</v>
+        <v>-0.3179</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.043</v>
+        <v>-0.8316</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6019</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9716</v>
+        <v>-1.1573</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1503</v>
+        <v>-0.6037</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1787</v>
+        <v>-0.5535</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0507</v>
+        <v>-0.1939</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0434</v>
+        <v>-0.3627</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0073</v>
+        <v>0.1688</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4141</v>
+        <v>-0.8114</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4141</v>
+        <v>-2.0587</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6674</v>
+        <v>-3.0703</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.465</v>
+        <v>-4.147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7976</v>
+        <v>1.0767</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6555</v>
+        <v>-2.6705</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0074</v>
+        <v>-0.0023</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6629</v>
+        <v>-2.6681</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4912</v>
+        <v>-2.5317</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1345</v>
+        <v>0.1132</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6257</v>
+        <v>-2.6449</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1644</v>
+        <v>-0.1387</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0387</v>
+        <v>-0.4275</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2511</v>
+        <v>-0.386</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2898</v>
+        <v>-0.0414</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.8829</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9135</v>
+        <v>-3.1016</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3463</v>
+        <v>-1.4591</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5672</v>
+        <v>-1.6425</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7748</v>
+        <v>-2.7749</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5064</v>
+        <v>0.5083</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.2813</v>
+        <v>-3.2832</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4586</v>
+        <v>-1.4726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3162</v>
+        <v>-1.3023</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3396</v>
+        <v>0.1498</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0484</v>
+        <v>-0.1443</v>
       </c>
       <c r="U8" t="n">
-        <v>0.388</v>
+        <v>0.294</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7503</v>
+        <v>-3.1747</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4104</v>
+        <v>-4.2923</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3399</v>
+        <v>1.1177</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5806</v>
+        <v>-3.1831</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1675</v>
+        <v>-1.528</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4131</v>
+        <v>-1.6551</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1066</v>
+        <v>-2.7009</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0693</v>
+        <v>-1.4414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>-1.2595</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6871</v>
+        <v>-0.4822</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2368</v>
+        <v>-0.0866</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4504</v>
+        <v>-0.3956</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4231</v>
+        <v>0.1173</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1825</v>
+        <v>-0.2257</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7594</v>
+        <v>0.343</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8719</v>
+        <v>-3.7319</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9932</v>
+        <v>-3.0696</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1213</v>
+        <v>-0.6623</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1822</v>
+        <v>-0.5644</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5296</v>
+        <v>-0.1612</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6526</v>
+        <v>-0.4033</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6765</v>
+        <v>0.1062</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4342</v>
+        <v>0.0689</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2423</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5057</v>
+        <v>-0.6706</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0954</v>
+        <v>-0.2301</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4104</v>
+        <v>-0.4405</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5804</v>
+        <v>-0.4147</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9557</v>
+        <v>-0.8296</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3753</v>
+        <v>0.4149</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1093</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1093</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4113</v>
+        <v>-4.5668</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1219</v>
+        <v>-5.5603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7106</v>
+        <v>0.9935</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.707</v>
+        <v>-1.7144</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2164</v>
+        <v>-1.215</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4905</v>
+        <v>-0.4994</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0499</v>
+        <v>-1.0862</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9838</v>
+        <v>-1.0065</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.657</v>
+        <v>-0.6282</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8897</v>
+        <v>-1.0314</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4426</v>
+        <v>-0.832</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.447</v>
+        <v>-0.1994</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7636</v>
+        <v>-10.7331</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.795300000000001</v>
+        <v>-9.078399999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9683</v>
+        <v>-1.6546</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.0113</v>
+        <v>-8.0204</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1206</v>
+        <v>-2.1522</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.8905</v>
+        <v>-5.8682</v>
       </c>
       <c r="J12" t="n">
-        <v>1.734400000000001</v>
+        <v>1.480000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.107600000000001</v>
+        <v>3.9573</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3734</v>
+        <v>-2.477400000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.7456</v>
+        <v>-9.500299999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.228399999999999</v>
+        <v>-6.1096</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.5175</v>
+        <v>-3.3907</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R12" t="n">
-        <v>13.6102</v>
+        <v>13.6581</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4347</v>
+        <v>-1.3942</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.961700000000001</v>
+        <v>-2.9076</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5271</v>
+        <v>1.5134</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3176</v>
+        <v>-1.3186</v>
       </c>
       <c r="W12" t="n">
-        <v>6.042</v>
+        <v>6.007</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.359700000000001</v>
+        <v>-7.325600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0542</v>
+        <v>5.8004</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4577</v>
+        <v>5.0122</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5965</v>
+        <v>0.7882</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7907</v>
+        <v>3.7901</v>
       </c>
       <c r="H13" t="n">
-        <v>0.792</v>
+        <v>0.8008</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9986</v>
+        <v>2.9892</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9513</v>
+        <v>4.9209</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9741</v>
+        <v>1.965</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9772</v>
+        <v>2.9559</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1606</v>
+        <v>-1.1309</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8045</v>
+        <v>-0.058</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9739</v>
+        <v>-0.3836</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1693</v>
+        <v>0.3256</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5566</v>
+        <v>4.7514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.596</v>
+        <v>1.9657</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9606</v>
+        <v>2.7857</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0949</v>
+        <v>4.0975</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8527</v>
+        <v>2.852</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2422</v>
+        <v>1.2455</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5206</v>
+        <v>3.4899</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5558</v>
+        <v>2.5371</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5743</v>
+        <v>0.6076</v>
       </c>
       <c r="N14" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.369</v>
+        <v>0.5644</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2511</v>
+        <v>-0.3373</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1179</v>
+        <v>0.9018</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0903</v>
+        <v>3.9495</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1131</v>
+        <v>1.9702</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9772</v>
+        <v>1.9794</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2386</v>
+        <v>3.2453</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8903</v>
+        <v>0.8931</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3484</v>
+        <v>2.3523</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3421</v>
+        <v>2.3235</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7029</v>
+        <v>0.6927</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8965</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6929</v>
+        <v>0.5448</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1875</v>
+        <v>-0.3046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8804</v>
+        <v>0.8495</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5978</v>
+        <v>3.5964</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1881</v>
+        <v>-0.3111</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7859</v>
+        <v>3.9074</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3995</v>
+        <v>2.4181</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6535</v>
+        <v>0.6629</v>
       </c>
       <c r="I16" t="n">
-        <v>1.746</v>
+        <v>1.7552</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9226</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L16" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4746</v>
+        <v>1.4955</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O16" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8807</v>
+        <v>0.8596</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8595</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5591</v>
+        <v>1.9625</v>
       </c>
       <c r="E17" t="n">
-        <v>1.649</v>
+        <v>-0.764</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08989999999999999</v>
+        <v>2.7265</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5565</v>
+        <v>0.0716</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3912</v>
+        <v>1.1861</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1653</v>
+        <v>-1.1145</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6025</v>
+        <v>-0.3897</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>1.5029</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6371</v>
+        <v>-1.8925</v>
       </c>
       <c r="M17" t="n">
-        <v>0.046</v>
+        <v>0.4613</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4258</v>
+        <v>-0.3168</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4718</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>0.728</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2249</v>
+        <v>-0.1467</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4969</v>
+        <v>0.9889</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5385</v>
+        <v>0.9509</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5606</v>
+        <v>0.9335</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0991</v>
+        <v>0.0175</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0757</v>
+        <v>-0.5494</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1846</v>
+        <v>-0.3825</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1089</v>
+        <v>-0.1669</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3599</v>
+        <v>-0.6062</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5168</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8767</v>
+        <v>-0.6407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4356</v>
+        <v>0.0568</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3321</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7678</v>
+        <v>0.4738</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4213</v>
+        <v>0.1149</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>0.5201</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3951</v>
+        <v>-0.4052</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1059</v>
+        <v>-0.0871</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6762</v>
+        <v>-1.1556</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7821</v>
+        <v>1.0685</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4398</v>
+        <v>0.4379</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4162</v>
+        <v>0.2276</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6472</v>
+        <v>0.1765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2311</v>
+        <v>0.0512</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6575</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4836</v>
+        <v>1.1268</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1411</v>
+        <v>-1.6374</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8356</v>
+        <v>1.0664</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.6678</v>
+        <v>-0.2818</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1679</v>
+        <v>1.3482</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2777</v>
+        <v>2.3407</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.5016</v>
+        <v>0.71</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2239</v>
+        <v>1.6308</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5579</v>
+        <v>-1.2744</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1662</v>
+        <v>-0.9918</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.2826</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4711</v>
+        <v>-0.5574</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4548</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0163</v>
+        <v>0.0631</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6675</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4141</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8154</v>
+        <v>-1.6958</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7977</v>
+        <v>-0.6249</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6131</v>
+        <v>-1.0709</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0574</v>
+        <v>-3.8418</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2887</v>
+        <v>-3.6813</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3461</v>
+        <v>-0.1606</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3594</v>
+        <v>-2.3081</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7202</v>
+        <v>-2.5315</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6392</v>
+        <v>0.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.302</v>
+        <v>-1.5337</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0089</v>
+        <v>-1.1497</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2931</v>
+        <v>-0.384</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8462</v>
+        <v>0.4436</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9739</v>
+        <v>0.3968</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1276</v>
+        <v>0.0468</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>2.6522</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9857</v>
+        <v>-1.8104</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3405</v>
+        <v>-1.1084</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6452</v>
+        <v>-0.702</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7221</v>
+        <v>-0.7163</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1703</v>
+        <v>-0.1668</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.794</v>
+        <v>-0.7881</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1294</v>
+        <v>0.0441</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>-0.0419</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5133</v>
+        <v>-2.1655</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9036</v>
+        <v>-2.5733</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3903</v>
+        <v>0.4079</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4536</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5442</v>
+        <v>-0.532</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0905</v>
+        <v>0.0784</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0785</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0081</v>
+        <v>-0.023</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5321</v>
+        <v>-0.5168</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4718</v>
+        <v>-0.1184</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0151</v>
+        <v>0.0141</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.767</v>
+        <v>-2.1734</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.46</v>
+        <v>-2.8165</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6929</v>
+        <v>0.6431</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6748</v>
+        <v>-1.7032</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6524</v>
+        <v>0.6438</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3272</v>
+        <v>-2.347</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0737</v>
+        <v>-1.1343</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0004</v>
+        <v>0.975</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0741</v>
+        <v>-2.1094</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6011</v>
+        <v>-0.5689</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2925</v>
+        <v>0.3218</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2521</v>
+        <v>-0.544</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9596</v>
+        <v>0.8658</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.7635</v>
+        <v>12.5683</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9681</v>
+        <v>1.654600000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>9.795299999999999</v>
+        <v>10.9139</v>
       </c>
       <c r="G25" t="n">
-        <v>8.011200000000001</v>
+        <v>8.020499999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1206</v>
+        <v>2.1522</v>
       </c>
       <c r="I25" t="n">
-        <v>5.890600000000001</v>
+        <v>5.8681</v>
       </c>
       <c r="J25" t="n">
-        <v>9.745699999999999</v>
+        <v>9.500300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2283</v>
+        <v>6.109800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.5173</v>
+        <v>3.390600000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7343</v>
+        <v>-1.4801</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.1076</v>
+        <v>-3.9574</v>
       </c>
       <c r="O25" t="n">
-        <v>2.373</v>
+        <v>2.4772</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-4.996003610813204e-16</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R25" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4348</v>
+        <v>3.2292</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.527199999999999</v>
+        <v>-1.5133</v>
       </c>
       <c r="U25" t="n">
-        <v>3.9616</v>
+        <v>4.7427</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W25" t="n">
-        <v>7.3597</v>
+        <v>7.3256</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.042000000000001</v>
+        <v>-6.006900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104676_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104676_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.0587</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.325600000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104676_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.006900000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
